--- a/Calc Simples - ARREMATAI.xlsx
+++ b/Calc Simples - ARREMATAI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/78b8298400c0454e/ARREMATAI/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python\arrematai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6193E1ED-C3BB-47A6-9D9A-4CCA0A2E3F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C6E016-57B4-41D3-ABE2-600635351DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{AC9232A4-AAE0-4ED4-9E5A-EF6B137CDC7B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{AC9232A4-AAE0-4ED4-9E5A-EF6B137CDC7B}"/>
   </bookViews>
   <sheets>
     <sheet name="CalcSimples" sheetId="1" r:id="rId1"/>
@@ -20,30 +20,19 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -58,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="34">
   <si>
     <t>Calculadora de Viabilidade - Simples</t>
   </si>
@@ -105,27 +94,6 @@
     <t>Selecione o motivo do leilão do automóvel. Calcularemos o melhor preço de venda considerando o motivo de leilão do veículo.</t>
   </si>
   <si>
-    <t>Cc</t>
-  </si>
-  <si>
-    <t>Custo</t>
-  </si>
-  <si>
-    <t>Valor dos custos estimados com reparos e transporte do veículo até sua oficina de confiança.</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>Lucro Minimo</t>
-  </si>
-  <si>
-    <t>Lista 2- Selecionada pelo usuário - Se "venda", permitir preenchimento do campo</t>
-  </si>
-  <si>
-    <t>Se for marcado como venda, preencha o valor do lucro mínino esperado com o veículo.</t>
-  </si>
-  <si>
     <t>%</t>
   </si>
   <si>
@@ -178,6 +146,9 @@
   </si>
   <si>
     <t>Valor do lucro esperado</t>
+  </si>
+  <si>
+    <t>50000 - 1000 * 1,05</t>
   </si>
 </sst>
 </file>
@@ -265,7 +236,44 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -372,12 +380,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3373331A-33D6-42DF-911E-414133C69396}" name="Tabela15" displayName="Tabela15" ref="B5:G12" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="B5:G12" xr:uid="{96CC35E0-692E-4DB5-BA40-874DB98BEE60}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3373331A-33D6-42DF-911E-414133C69396}" name="Tabela15" displayName="Tabela15" ref="B5:G10" totalsRowShown="0" headerRowDxfId="3">
+  <autoFilter ref="B5:G10" xr:uid="{96CC35E0-692E-4DB5-BA40-874DB98BEE60}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{E276E0D2-6FB1-4581-827C-F34AA1E7EEF4}" name="Códgio"/>
     <tableColumn id="2" xr3:uid="{E826F8FB-E381-4CD1-9E32-FB69CE36FE10}" name="Nome"/>
-    <tableColumn id="3" xr3:uid="{B7275951-0CEE-452D-B58D-6AFD9CAFEEC6}" name="Exemplo" dataDxfId="0" dataCellStyle="Porcentagem"/>
+    <tableColumn id="3" xr3:uid="{B7275951-0CEE-452D-B58D-6AFD9CAFEEC6}" name="Exemplo" dataDxfId="2" dataCellStyle="Porcentagem"/>
     <tableColumn id="4" xr3:uid="{7F5DAB7F-003B-45D2-BA1C-D270BD2E5D6F}" name="Seleção Exemplo"/>
     <tableColumn id="5" xr3:uid="{8DBE3C24-3D5C-4E34-87C9-B9284EEB370F}" name="Interação Usuário"/>
     <tableColumn id="6" xr3:uid="{60036E0E-0498-41FB-BA11-551015B0D1C4}" name="Dicas"/>
@@ -387,26 +395,42 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5F2C873B-5A68-4536-8F71-5BA0E52E9121}" name="Tabela26" displayName="Tabela26" ref="B17:F18" totalsRowShown="0">
-  <autoFilter ref="B17:F18" xr:uid="{DE8C6CB7-E9BF-4C86-9986-B7D941CB4C1C}"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5F2C873B-5A68-4536-8F71-5BA0E52E9121}" name="Tabela26" displayName="Tabela26" ref="B15:G16" totalsRowShown="0">
+  <autoFilter ref="B15:G16" xr:uid="{DE8C6CB7-E9BF-4C86-9986-B7D941CB4C1C}"/>
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{A8A695ED-5FC6-418D-9C20-8C31FADE9F56}" name="Lista 1 "/>
     <tableColumn id="2" xr3:uid="{C5958902-C14F-4B7C-BF49-F1E8F45637ED}" name="Financimamento"/>
     <tableColumn id="3" xr3:uid="{E9B223D5-3F71-455B-8400-493EFB32692A}" name="Pequena Monta"/>
     <tableColumn id="4" xr3:uid="{9E590107-4D3F-42AC-A217-1620604D2153}" name="Média Monta"/>
     <tableColumn id="5" xr3:uid="{F5A4800C-4B8A-465D-A6CB-8457642046DD}" name="Outros"/>
+    <tableColumn id="6" xr3:uid="{E562EB7E-FC17-4408-A06A-5D3B5BB252EB}" name="50000 - 1000 * 1,05"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{87199EA5-2A94-45E9-BDD9-FFFCDFB17D55}" name="Tabela37" displayName="Tabela37" ref="B20:D21" totalsRowShown="0">
-  <autoFilter ref="B20:D21" xr:uid="{116FE127-52E7-42D5-9E09-239D6FBC4EB5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{87199EA5-2A94-45E9-BDD9-FFFCDFB17D55}" name="Tabela37" displayName="Tabela37" ref="B18:D19" totalsRowShown="0">
+  <autoFilter ref="B18:D19" xr:uid="{116FE127-52E7-42D5-9E09-239D6FBC4EB5}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{9C3CDE14-85C7-4E5A-9265-8406BEE7884E}" name="Lista 2"/>
     <tableColumn id="2" xr3:uid="{0A0F3617-B1B9-4F8F-994E-F86228424E94}" name="Uso"/>
     <tableColumn id="3" xr3:uid="{07498151-AA2A-4898-8C5A-2BE0028162A3}" name="Venda"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3BA067E9-936F-47DC-A06E-20D51764ADA9}" name="Tabela155" displayName="Tabela155" ref="B23:G28" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="B23:G28" xr:uid="{3BA067E9-936F-47DC-A06E-20D51764ADA9}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{9A97AF9D-3827-49ED-BB87-E467DF100498}" name="Códgio"/>
+    <tableColumn id="2" xr3:uid="{7FB92A35-D578-4CC8-B234-3ECAE4244C95}" name="Nome"/>
+    <tableColumn id="3" xr3:uid="{3CF95083-EE54-487B-B2E6-FC40D47D1385}" name="Exemplo" dataDxfId="0" dataCellStyle="Porcentagem"/>
+    <tableColumn id="4" xr3:uid="{00B7456C-A06E-4A56-B84F-C2B965898A03}" name="Seleção Exemplo"/>
+    <tableColumn id="5" xr3:uid="{AD5135FF-1056-4DC1-B320-D47248BC5EC1}" name="Interação Usuário"/>
+    <tableColumn id="6" xr3:uid="{C17654B4-DA28-4F48-BE02-7C3EF70CF31C}" name="Dicas"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -729,7 +753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{504D4195-FEB1-4CF9-A14B-0B4660D21F59}">
-  <dimension ref="B2:G21"/>
+  <dimension ref="B2:G28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="30.28515625" bestFit="1" customWidth="1"/>
@@ -779,7 +803,7 @@
         <v>7</v>
       </c>
       <c r="D6" s="5">
-        <v>100000</v>
+        <v>95085</v>
       </c>
       <c r="F6" t="s">
         <v>8</v>
@@ -797,7 +821,7 @@
       </c>
       <c r="D7" s="5" cm="1">
         <f t="array" ref="D7">D6*(1-Tabela26[Pequena Monta])</f>
-        <v>88200</v>
+        <v>83864.97</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -816,8 +840,8 @@
       <c r="C8" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="5">
-        <v>8000</v>
+      <c r="D8">
+        <v>0.05</v>
       </c>
       <c r="F8" t="s">
         <v>8</v>
@@ -834,130 +858,210 @@
         <v>19</v>
       </c>
       <c r="D9" s="5">
-        <f>0.05*D7</f>
-        <v>4410</v>
+        <v>2000</v>
       </c>
       <c r="F9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" t="s">
         <v>20</v>
-      </c>
-      <c r="G9" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
         <v>22</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" s="5">
+        <f>(D7-D9)/1.05</f>
+        <v>77966.638095238086</v>
+      </c>
+      <c r="F10" t="s">
         <v>23</v>
       </c>
-      <c r="D10">
-        <v>0.05</v>
-      </c>
-      <c r="F10" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" t="s">
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
+      <c r="C13" t="s">
         <v>25</v>
       </c>
-      <c r="C11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="5">
-        <v>2000</v>
-      </c>
-      <c r="F11" t="s">
-        <v>8</v>
-      </c>
-      <c r="G11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="5">
-        <f>(D7-D8-D9-D11)/1.05</f>
-        <v>70276.190476190473</v>
-      </c>
-      <c r="F12" t="s">
-        <v>30</v>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C16">
+        <v>5.5E-2</v>
+      </c>
+      <c r="D16">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="E16">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="F16">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" t="s">
         <v>31</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" t="s">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="5">
+        <v>95085</v>
+      </c>
+      <c r="F24" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="5">
+        <v>50000</v>
+      </c>
+      <c r="E25" t="s">
         <v>12</v>
       </c>
-      <c r="E17" t="s">
-        <v>35</v>
-      </c>
-      <c r="F17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C18">
-        <v>5.5E-2</v>
-      </c>
-      <c r="D18">
-        <v>0.11799999999999999</v>
-      </c>
-      <c r="E18">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="F18">
-        <v>5.5E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21" t="s">
-        <v>39</v>
+      <c r="F25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26">
+        <v>0.05</v>
+      </c>
+      <c r="F26" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="5">
+        <v>1000</v>
+      </c>
+      <c r="F27" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28" s="5">
+        <f>(D25-D27)/1.05</f>
+        <v>46666.666666666664</v>
+      </c>
+      <c r="F28" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
-  <tableParts count="3">
+  <tableParts count="4">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>